--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/mar-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/mar-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>28212.27</v>
+        <v>29458.18</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>17856.86</v>
+        <v>18645.45</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>40443.19</v>
+        <v>42229.25</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>13734.61</v>
+        <v>14341.16</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>17672.59</v>
+        <v>18185.92</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10494.15</v>
+        <v>10798.97</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>28051.64</v>
+        <v>28866.44</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8568.48</v>
+        <v>8602.26</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11675.27</v>
+        <v>11721.3</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8960.049999999999</v>
+        <v>8995.379999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10490.71</v>
+        <v>10532.07</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>16606.09</v>
+        <v>16671.56</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11908.33</v>
+        <v>11955.28</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>43163.45</v>
+        <v>43874.85</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>11910.56</v>
+        <v>11939.87</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11368.09</v>
+        <v>11396.06</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>40493.86</v>
+        <v>40593.49</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>19440.79</v>
+        <v>19488.62</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>20272.95</v>
+        <v>20011.96</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>8786.120000000001</v>
+        <v>8724.120000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>23054</v>
+        <v>23415.13</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>9969.780000000001</v>
+        <v>9969.27</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>22215.1</v>
+        <v>22213.96</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>44446.14</v>
+        <v>44247.4</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>28229.9</v>
+        <v>28254.22</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>40921.83</v>
+        <v>40957.09</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>30101.05</v>
+        <v>30126.98</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>37352.21</v>
+        <v>37384.39</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8880.01</v>
+        <v>8887.66</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>5527.46</v>
+        <v>5550.29</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>6040.89</v>
+        <v>6065.84</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>52194.66</v>
+        <v>52050.69</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>12849.78</v>
+        <v>12814.34</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>24461.13</v>
+        <v>24178.74</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>19138.85</v>
+        <v>18853.39</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>13333.36</v>
+        <v>13256.77</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>7395.24</v>
+        <v>7347.86</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>21477.51</v>
+        <v>21384.99</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>8636.940000000001</v>
+        <v>8599.73</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>13861.28</v>
+        <v>13801.56</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>12572.46</v>
+        <v>12279.91</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/mar-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/mar-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/mar-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/mar-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SE</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO OCCIDENTE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/mar-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/mar-2026.xlsx
@@ -623,7 +623,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>77.043.435-1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1448,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1513,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1639,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1704,11 @@
           <t>77.547.481-5</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1891,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1956,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2082,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2330,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2395,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2460,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2586,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2651,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2960,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
